--- a/Result/profitability/5228.xlsx
+++ b/Result/profitability/5228.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM45"/>
+  <dimension ref="A1:AM46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.96</v>
       </c>
       <c r="M2" t="n">
-        <v>0.13125</v>
+        <v>0.28375</v>
       </c>
       <c r="N2" t="n">
-        <v>19.61125</v>
+        <v>22.63875</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-0.62</v>
       </c>
       <c r="M3" t="n">
-        <v>0.105</v>
+        <v>0.24125</v>
       </c>
       <c r="N3" t="n">
-        <v>20.0325</v>
+        <v>21.9825</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -6145,6 +6145,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>5228</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>201</v>
+      </c>
+      <c r="D46" t="n">
+        <v>138</v>
+      </c>
+      <c r="E46" t="n">
+        <v>64</v>
+      </c>
+      <c r="F46" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="G46" t="n">
+        <v>31</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>15.39%</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J46" t="n">
+        <v>30</v>
+      </c>
+      <c r="K46" t="n">
+        <v>31</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.1125</v>
+      </c>
+      <c r="N46" t="n">
+        <v>20.77</v>
+      </c>
+      <c r="O46" t="n">
+        <v>1</v>
+      </c>
+      <c r="P46" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W46" t="n">
+        <v>-0.1799999999999999</v>
+      </c>
+      <c r="X46" t="n">
+        <v>-0.1818181818181818</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>-5.75</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>-0.1539491298527443</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>-3.314285714285715</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>20.04</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>1.733564013840831</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK46" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
